--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_52_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_52_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4496</v>
+        <v>4.2142</v>
       </c>
       <c r="E2" t="n">
-        <v>2.242</v>
+        <v>2.6705</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2076</v>
+        <v>1.5437</v>
       </c>
       <c r="G2" t="n">
         <v>3.3774</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3917</v>
+        <v>-0.6271</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4446</v>
+        <v>-0.1085</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0425</v>
+        <v>2.8161</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0024</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0401</v>
+        <v>2.2672</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4482</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4907</v>
+        <v>0.2642</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.955</v>
+        <v>-0.4086</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4458</v>
+        <v>0.6728</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7463</v>
+        <v>2.6907</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5997</v>
+        <v>1.6521</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1466</v>
+        <v>1.0386</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7858</v>
+        <v>1.997</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3409</v>
+        <v>0.6519</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4449</v>
+        <v>1.3451</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6026</v>
+        <v>2.172</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.897</v>
+        <v>0.8739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2944</v>
+        <v>1.2981</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1833</v>
+        <v>-0.175</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4439</v>
+        <v>-0.222</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9058</v>
+        <v>-0.3785</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0578</v>
+        <v>-0.2003</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.152</v>
+        <v>-0.1781</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0026</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0647</v>
+        <v>2.3417</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7471</v>
+        <v>1.0577</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3175</v>
+        <v>1.2839</v>
       </c>
       <c r="G5" t="n">
         <v>2.3115</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5689</v>
+        <v>-0.2919</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>-0.4283</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.1364</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1418</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9837</v>
+        <v>2.1058</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1803</v>
+        <v>1.892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8034</v>
+        <v>0.2138</v>
       </c>
       <c r="G6" t="n">
-        <v>1.997</v>
+        <v>-1.7858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6519</v>
+        <v>-1.3409</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3451</v>
+        <v>-0.4449</v>
       </c>
       <c r="J6" t="n">
-        <v>2.172</v>
+        <v>-0.6026</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8739</v>
+        <v>-0.897</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2981</v>
+        <v>0.2944</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.175</v>
+        <v>-1.1833</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.222</v>
+        <v>-0.4439</v>
       </c>
       <c r="O6" t="n">
-        <v>0.047</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0855</v>
+        <v>0.2653</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>0.3501</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4134</v>
+        <v>-0.0848</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>2.0026</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8192</v>
+        <v>2.0467</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5646</v>
+        <v>0.0999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3837</v>
+        <v>1.9469</v>
       </c>
       <c r="G7" t="n">
         <v>3.9313</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3624</v>
+        <v>-0.1349</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1123</v>
+        <v>-0.4479</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7499</v>
+        <v>0.313</v>
       </c>
       <c r="V7" t="n">
         <v>1.4975</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>S. MILJENOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3015</v>
+        <v>1.4154</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1703</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4718</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5094</v>
+        <v>1.4249</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0599</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5693</v>
+        <v>0.6291</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1067</v>
+        <v>0.8066</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4271</v>
+        <v>0.8066</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6796</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.6183</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.487</v>
+        <v>-0.0108</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1103</v>
+        <v>0.6291</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1204</v>
+        <v>-0.1513</v>
       </c>
       <c r="T8" t="n">
-        <v>0.13</v>
+        <v>-0.1808</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2504</v>
+        <v>0.0294</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. MILJENOVIC</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2302</v>
+        <v>1.3687</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6497000000000001</v>
+        <v>-0.1703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5805</v>
+        <v>1.539</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4249</v>
+        <v>1.5094</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7959000000000001</v>
+        <v>-0.0599</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6291</v>
+        <v>1.5693</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8066</v>
+        <v>2.1067</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8066</v>
+        <v>0.4271</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.6796</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6183</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0108</v>
+        <v>-0.487</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>-0.1103</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3365</v>
+        <v>-0.0532</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>0.13</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0378</v>
+        <v>-0.1832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1304</v>
+        <v>-0.0258</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0299</v>
+        <v>-2.288</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1602</v>
+        <v>2.2622</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5884</v>
+        <v>-2.5587</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6421</v>
+        <v>-0.6915</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0536</v>
+        <v>-1.8671</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8285</v>
+        <v>-3.2699</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3662</v>
+        <v>-0.9845</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4623</v>
+        <v>-2.2854</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2401</v>
+        <v>0.7113</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2759</v>
+        <v>0.293</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5159</v>
+        <v>0.4183</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3993</v>
+        <v>-0.114</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0306</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6313</v>
+        <v>-0.0237</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>1.719</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0672</v>
+        <v>-0.4704</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5585</v>
+        <v>-2.1347</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4913</v>
+        <v>1.6643</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1204</v>
+        <v>-0.5884</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6421</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7529</v>
+        <v>0.0536</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6623</v>
+        <v>-1.8285</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7359</v>
+        <v>-0.3662</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0736</v>
+        <v>-1.4623</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7827</v>
+        <v>1.2401</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1034</v>
+        <v>-0.2759</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6793</v>
+        <v>1.5159</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2763</v>
+        <v>-0.2014</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4955</v>
+        <v>-0.0743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2192</v>
+        <v>-0.1272</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1438</v>
+        <v>-0.5726</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.406</v>
+        <v>-2.0303</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2622</v>
+        <v>1.4577</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5587</v>
+        <v>0.1204</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6915</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8671</v>
+        <v>0.7529</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2699</v>
+        <v>-0.6623</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9845</v>
+        <v>-0.7359</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2854</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7113</v>
+        <v>0.7827</v>
       </c>
       <c r="N12" t="n">
-        <v>0.293</v>
+        <v>0.1034</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4183</v>
+        <v>0.6793</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.232</v>
+        <v>-0.2291</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.0237</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0237</v>
+        <v>-0.2528</v>
       </c>
       <c r="V12" t="n">
-        <v>1.719</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.55710000000001</v>
+        <v>17.93049999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.691900000000001</v>
+        <v>2.065399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15.8649</v>
+        <v>15.865</v>
       </c>
       <c r="G13" t="n">
         <v>8.290800000000001</v>
@@ -1441,10 +1441,10 @@
         <v>9.184999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>6.845099999999999</v>
+        <v>6.8451</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2378999999999999</v>
+        <v>0.2379000000000002</v>
       </c>
       <c r="L13" t="n">
         <v>6.6073</v>
@@ -1459,7 +1459,7 @@
         <v>2.5776</v>
       </c>
       <c r="P13" t="n">
-        <v>2.319500000000001</v>
+        <v>2.3195</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7575</v>
@@ -1468,10 +1468,10 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0253</v>
+        <v>-1.6519</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2184</v>
+        <v>-1.8453</v>
       </c>
       <c r="U13" t="n">
         <v>0.1932999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7304</v>
+        <v>4.7191</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6271</v>
+        <v>5.3348</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.6158</v>
       </c>
       <c r="G14" t="n">
         <v>4.2093</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1901</v>
+        <v>-0.2014</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.187</v>
+        <v>-0.4793</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0031</v>
+        <v>0.2779</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6083</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1697</v>
+        <v>0.6398</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.663</v>
+        <v>1.5244</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8327</v>
+        <v>-0.8845</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2904</v>
+        <v>1.3847</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0155</v>
+        <v>0.8428</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2749</v>
+        <v>0.5419</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.5191</v>
+        <v>3.69</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0168</v>
+        <v>1.4116</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5359</v>
+        <v>2.2784</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2287</v>
+        <v>-2.3053</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0323</v>
+        <v>-0.5688</v>
       </c>
       <c r="O15" t="n">
-        <v>0.261</v>
+        <v>-1.7365</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3879</v>
+        <v>0.183</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2161</v>
+        <v>0.0121</v>
       </c>
       <c r="U15" t="n">
-        <v>0.604</v>
+        <v>0.1709</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0589</v>
+        <v>0.1425</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5606</v>
+        <v>-0.5451</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6195</v>
+        <v>0.6875</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1989</v>
+        <v>-1.2904</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2486</v>
+        <v>-0.0155</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9503</v>
+        <v>-1.2749</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.928</v>
+        <v>-1.5191</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.981</v>
+        <v>0.0168</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.947</v>
+        <v>-1.5359</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7292</v>
+        <v>0.2287</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0033</v>
+        <v>0.261</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0258</v>
+        <v>0.3607</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5272</v>
+        <v>-0.0982</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4986</v>
+        <v>0.4589</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.253</v>
+        <v>-0.1992</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6987</v>
+        <v>-3.0324</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9517</v>
+        <v>2.8332</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3847</v>
+        <v>-1.1989</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8428</v>
+        <v>-0.2486</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5419</v>
+        <v>-0.9503</v>
       </c>
       <c r="J17" t="n">
-        <v>3.69</v>
+        <v>-1.928</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4116</v>
+        <v>-0.981</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2784</v>
+        <v>-0.947</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3053</v>
+        <v>0.7292</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5688</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7365</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7099</v>
+        <v>0.7677</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8136</v>
+        <v>0.0553</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1037</v>
+        <v>0.7123</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.725</v>
+        <v>-0.3883</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1442</v>
+        <v>0.3801</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8693</v>
+        <v>-0.7685</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6508</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0742</v>
+        <v>0.2625</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1415</v>
+        <v>0.0944</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2814</v>
+        <v>-0.5299</v>
       </c>
       <c r="E19" t="n">
         <v>-2.203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9216</v>
+        <v>1.6731</v>
       </c>
       <c r="G19" t="n">
         <v>1.875</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8369</v>
+        <v>-0.0854</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2592</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5777</v>
+        <v>0.1737</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8296</v>
+        <v>-2.3128</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4989</v>
+        <v>-1.2066</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3307</v>
+        <v>-1.1062</v>
       </c>
       <c r="G20" t="n">
         <v>0.2799</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3776</v>
+        <v>0.8944</v>
       </c>
       <c r="T20" t="n">
-        <v>0.767</v>
+        <v>0.0593</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6106</v>
+        <v>0.8351</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7912</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8036</v>
+        <v>-2.3762</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6654</v>
+        <v>-1.1936</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1382</v>
+        <v>-1.1826</v>
       </c>
       <c r="G21" t="n">
         <v>-1.192</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1564</v>
+        <v>0.5838</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3576</v>
+        <v>0.1142</v>
       </c>
       <c r="U21" t="n">
-        <v>0.514</v>
+        <v>0.4696</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8523</v>
+        <v>-3.3809</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7294</v>
+        <v>-3.3973</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1229</v>
+        <v>0.0164</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9167</v>
+        <v>0.4473</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.749</v>
+        <v>1.3206</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1677</v>
+        <v>-0.8733</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8085</v>
+        <v>0.2115</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1694</v>
+        <v>0.9243</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6391</v>
+        <v>-0.7127</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1082</v>
+        <v>0.2358</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5796</v>
+        <v>0.3963</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5286</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9278</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.281</v>
+        <v>0.2388</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2388</v>
+        <v>-0.1296</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0422</v>
+        <v>0.3684</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1444</v>
+        <v>-0.8197</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.15</v>
+        <v>-3.448</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6395</v>
+        <v>-3.2292</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5105</v>
+        <v>-0.2188</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0388</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5693</v>
+        <v>0.2713</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6018</v>
+        <v>0.0121</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0325</v>
+        <v>0.2592</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0093</v>
+        <v>-3.5651</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6332</v>
+        <v>-2.5551</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3761</v>
+        <v>-1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4473</v>
+        <v>-2.9167</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3206</v>
+        <v>-1.749</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8733</v>
+        <v>-1.1677</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2115</v>
+        <v>-1.8085</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9243</v>
+        <v>-1.1694</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7127</v>
+        <v>-0.6391</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2358</v>
+        <v>-1.1082</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3963</v>
+        <v>-0.5796</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1605</v>
+        <v>-0.5286</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.2473</v>
+        <v>0.9278</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3897</v>
+        <v>0.5682</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3655</v>
+        <v>0.4132</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0242</v>
+        <v>0.1551</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8197</v>
+        <v>-2.1444</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8197</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6118</v>
+        <v>-4.4989</v>
       </c>
       <c r="E25" t="n">
         <v>-5.742</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1303</v>
+        <v>1.2432</v>
       </c>
       <c r="G25" t="n">
         <v>-6.1994</v>
@@ -2404,13 +2404,13 @@
         <v>2.3195</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4279</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>0.0123</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4156</v>
+        <v>0.5285</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,43 +2437,43 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.557</v>
+        <v>-15.1979</v>
       </c>
       <c r="E26" t="n">
         <v>-15.865</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.692</v>
+        <v>0.6670000000000004</v>
       </c>
       <c r="G26" t="n">
         <v>-8.290800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8941000000000003</v>
+        <v>0.894099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-9.185</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.445799999999999</v>
+        <v>-1.445800000000002</v>
       </c>
       <c r="K26" t="n">
         <v>1.132</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.5776</v>
+        <v>-2.577599999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.844899999999999</v>
+        <v>-6.8449</v>
       </c>
       <c r="N26" t="n">
         <v>-0.2378</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.6072</v>
+        <v>-6.607200000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.319500000000001</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q26" t="n">
         <v>-15.0771</v>
@@ -2482,13 +2482,13 @@
         <v>12.7574</v>
       </c>
       <c r="S26" t="n">
-        <v>2.025100000000001</v>
+        <v>4.384399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1933999999999999</v>
+        <v>-0.1934</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2184</v>
+        <v>4.577599999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-8.9719</v>
@@ -2497,7 +2497,7 @@
         <v>0.8508</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.822699999999999</v>
+        <v>-9.822700000000001</v>
       </c>
     </row>
   </sheetData>
